--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/103.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/103.xlsx
@@ -426,13 +426,13 @@
         <v>-15.16705186318524</v>
       </c>
       <c r="E2">
-        <v>-9.313085110396161</v>
+        <v>-8.519732692044375</v>
       </c>
       <c r="F2">
-        <v>-4.596306854545137</v>
+        <v>-4.918492072189976</v>
       </c>
       <c r="G2">
-        <v>-5.592138259604291</v>
+        <v>-4.998004583307909</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.10160382169547</v>
       </c>
       <c r="E3">
-        <v>-9.961680328618755</v>
+        <v>-9.691593081853279</v>
       </c>
       <c r="F3">
-        <v>-4.363709571513064</v>
+        <v>-5.166818395466407</v>
       </c>
       <c r="G3">
-        <v>-5.273607499452235</v>
+        <v>-4.292994115810256</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.13819296053893</v>
       </c>
       <c r="E4">
-        <v>-11.56985013211868</v>
+        <v>-10.89914690379064</v>
       </c>
       <c r="F4">
-        <v>-4.81285451914797</v>
+        <v>-5.059298791685239</v>
       </c>
       <c r="G4">
-        <v>-5.076196358399955</v>
+        <v>-3.912605812256918</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.27020888655664</v>
       </c>
       <c r="E5">
-        <v>-12.00145898978974</v>
+        <v>-11.36254564899555</v>
       </c>
       <c r="F5">
-        <v>-4.583571534094498</v>
+        <v>-4.876255275056035</v>
       </c>
       <c r="G5">
-        <v>-5.6307988104119</v>
+        <v>-4.576780700527661</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.48463110926867</v>
       </c>
       <c r="E6">
-        <v>-11.51203510446276</v>
+        <v>-11.53165698233799</v>
       </c>
       <c r="F6">
-        <v>-4.548061080271288</v>
+        <v>-5.147184431285253</v>
       </c>
       <c r="G6">
-        <v>-4.389211811363634</v>
+        <v>-4.169159849368278</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.75264168227982</v>
       </c>
       <c r="E7">
-        <v>-13.06232648167065</v>
+        <v>-13.177657657698</v>
       </c>
       <c r="F7">
-        <v>-4.613382820186446</v>
+        <v>-4.782592601188898</v>
       </c>
       <c r="G7">
-        <v>-4.354729169026585</v>
+        <v>-4.648109714716798</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.052451197161</v>
       </c>
       <c r="E8">
-        <v>-14.94699585113091</v>
+        <v>-13.96803486862674</v>
       </c>
       <c r="F8">
-        <v>-4.254047809628257</v>
+        <v>-4.787012769650237</v>
       </c>
       <c r="G8">
-        <v>-4.833728692558194</v>
+        <v>-4.17346686911487</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.34711343922101</v>
       </c>
       <c r="E9">
-        <v>-15.1599428128676</v>
+        <v>-13.85794313702627</v>
       </c>
       <c r="F9">
-        <v>-4.744219309621614</v>
+        <v>-4.766104776403576</v>
       </c>
       <c r="G9">
-        <v>-5.059660183431296</v>
+        <v>-4.492053908541093</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.61133534330178</v>
       </c>
       <c r="E10">
-        <v>-15.75962145485934</v>
+        <v>-14.62353148123703</v>
       </c>
       <c r="F10">
-        <v>-4.342828086023294</v>
+        <v>-4.604097649968466</v>
       </c>
       <c r="G10">
-        <v>-4.460623589191253</v>
+        <v>-4.456753561455844</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.81059361810311</v>
       </c>
       <c r="E11">
-        <v>-16.04883697583322</v>
+        <v>-15.69558430391688</v>
       </c>
       <c r="F11">
-        <v>-4.090316022260517</v>
+        <v>-4.258948431183219</v>
       </c>
       <c r="G11">
-        <v>-4.286561725827452</v>
+        <v>-4.005456682996857</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.93002837437254</v>
       </c>
       <c r="E12">
-        <v>-17.13415822735554</v>
+        <v>-16.52666796770057</v>
       </c>
       <c r="F12">
-        <v>-4.073481111533424</v>
+        <v>-4.419795014887007</v>
       </c>
       <c r="G12">
-        <v>-4.40507925613336</v>
+        <v>-3.940493847879739</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.95094348342698</v>
       </c>
       <c r="E13">
-        <v>-18.78374092565561</v>
+        <v>-17.72243870026998</v>
       </c>
       <c r="F13">
-        <v>-3.658151778015599</v>
+        <v>-4.163729254966221</v>
       </c>
       <c r="G13">
-        <v>-4.020486559745149</v>
+        <v>-4.027604232654581</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.88085695199547</v>
       </c>
       <c r="E14">
-        <v>-20.12942679024895</v>
+        <v>-17.22321066871638</v>
       </c>
       <c r="F14">
-        <v>-3.846214372738365</v>
+        <v>-3.821531509237148</v>
       </c>
       <c r="G14">
-        <v>-4.41039930281497</v>
+        <v>-3.325318344135749</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.72680987675709</v>
       </c>
       <c r="E15">
-        <v>-20.10132760903135</v>
+        <v>-18.28908665284977</v>
       </c>
       <c r="F15">
-        <v>-3.120905815255952</v>
+        <v>-3.495696504815574</v>
       </c>
       <c r="G15">
-        <v>-4.001503891622968</v>
+        <v>-2.949005322141254</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.5153037245208</v>
       </c>
       <c r="E16">
-        <v>-20.89939416882512</v>
+        <v>-20.14290352889577</v>
       </c>
       <c r="F16">
-        <v>-3.087174694613956</v>
+        <v>-3.366785141224512</v>
       </c>
       <c r="G16">
-        <v>-4.0438755639801</v>
+        <v>-2.954302195004088</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.26629941260165</v>
       </c>
       <c r="E17">
-        <v>-21.01773678006757</v>
+        <v>-20.91030779118361</v>
       </c>
       <c r="F17">
-        <v>-2.655386529169908</v>
+        <v>-3.308139214208516</v>
       </c>
       <c r="G17">
-        <v>-3.676818827313407</v>
+        <v>-3.361025888322328</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.00434013340343</v>
       </c>
       <c r="E18">
-        <v>-22.31776204124156</v>
+        <v>-21.28605792197006</v>
       </c>
       <c r="F18">
-        <v>-2.047900809224682</v>
+        <v>-2.683925442931157</v>
       </c>
       <c r="G18">
-        <v>-3.57323847848069</v>
+        <v>-3.089869034837243</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.74183593654793</v>
       </c>
       <c r="E19">
-        <v>-23.61907791750774</v>
+        <v>-22.64769760049241</v>
       </c>
       <c r="F19">
-        <v>-1.793206825722932</v>
+        <v>-2.393402084156119</v>
       </c>
       <c r="G19">
-        <v>-3.886234006491084</v>
+        <v>-3.029577379476036</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.48848609322064</v>
       </c>
       <c r="E20">
-        <v>-24.79819292267693</v>
+        <v>-23.55451999205439</v>
       </c>
       <c r="F20">
-        <v>-1.369637721649461</v>
+        <v>-1.816600749545393</v>
       </c>
       <c r="G20">
-        <v>-3.902257046901156</v>
+        <v>-2.923411494577148</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.2465197318091</v>
       </c>
       <c r="E21">
-        <v>-25.49844444390502</v>
+        <v>-23.53977980915942</v>
       </c>
       <c r="F21">
-        <v>-1.301733132172374</v>
+        <v>-1.416015527429997</v>
       </c>
       <c r="G21">
-        <v>-3.827220221708036</v>
+        <v>-3.006641919979965</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.01622557500784</v>
       </c>
       <c r="E22">
-        <v>-25.93524293278887</v>
+        <v>-24.42312206299163</v>
       </c>
       <c r="F22">
-        <v>-0.4670113230259934</v>
+        <v>-1.422239880094632</v>
       </c>
       <c r="G22">
-        <v>-3.476944640379909</v>
+        <v>-3.594776887759188</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.79526982859529</v>
       </c>
       <c r="E23">
-        <v>-26.02929480945418</v>
+        <v>-24.57771510866549</v>
       </c>
       <c r="F23">
-        <v>-0.4609244793502227</v>
+        <v>-1.022145051481693</v>
       </c>
       <c r="G23">
-        <v>-3.850254997570285</v>
+        <v>-2.932227477348227</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.58013121795104</v>
       </c>
       <c r="E24">
-        <v>-26.55059462332116</v>
+        <v>-26.01123525511159</v>
       </c>
       <c r="F24">
-        <v>-0.1828846173353742</v>
+        <v>-0.5717078506984201</v>
       </c>
       <c r="G24">
-        <v>-4.488680462636576</v>
+        <v>-3.906448197553874</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.36984020463769</v>
       </c>
       <c r="E25">
-        <v>-27.41556938657826</v>
+        <v>-26.19925749591006</v>
       </c>
       <c r="F25">
-        <v>-0.2245581246354117</v>
+        <v>-0.4723940544093846</v>
       </c>
       <c r="G25">
-        <v>-4.382987985749804</v>
+        <v>-4.203122736055661</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-14.15963749290875</v>
       </c>
       <c r="E26">
-        <v>-26.65844928876185</v>
+        <v>-25.34591638237867</v>
       </c>
       <c r="F26">
-        <v>0.1364916064465724</v>
+        <v>-0.3592514926980142</v>
       </c>
       <c r="G26">
-        <v>-4.48852486699623</v>
+        <v>-4.164879313986001</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.95143610484842</v>
       </c>
       <c r="E27">
-        <v>-27.67728801337756</v>
+        <v>-25.69488058940975</v>
       </c>
       <c r="F27">
-        <v>0.08313646203225623</v>
+        <v>-0.1264761106743391</v>
       </c>
       <c r="G27">
-        <v>-5.394650976004607</v>
+        <v>-3.851738121971878</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.74007655232868</v>
       </c>
       <c r="E28">
-        <v>-26.93070567457699</v>
+        <v>-24.72627622696112</v>
       </c>
       <c r="F28">
-        <v>0.03689202340357103</v>
+        <v>-0.4361919138048378</v>
       </c>
       <c r="G28">
-        <v>-5.026899024774668</v>
+        <v>-4.620271337277067</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.52788806711931</v>
       </c>
       <c r="E29">
-        <v>-27.21191938197932</v>
+        <v>-25.4975478060515</v>
       </c>
       <c r="F29">
-        <v>0.003607392791684095</v>
+        <v>-0.4012389512437127</v>
       </c>
       <c r="G29">
-        <v>-5.029626914299027</v>
+        <v>-4.764253583871049</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.31031286869645</v>
       </c>
       <c r="E30">
-        <v>-27.05743049120764</v>
+        <v>-25.22237055450141</v>
       </c>
       <c r="F30">
-        <v>0.08000606161707689</v>
+        <v>-0.5667566987318875</v>
       </c>
       <c r="G30">
-        <v>-5.05977605252517</v>
+        <v>-4.129426681805946</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.09124048851354</v>
       </c>
       <c r="E31">
-        <v>-26.63337059970737</v>
+        <v>-24.92790653215264</v>
       </c>
       <c r="F31">
-        <v>0.2883172691338742</v>
+        <v>-0.1209310192799992</v>
       </c>
       <c r="G31">
-        <v>-5.390913370090771</v>
+        <v>-4.232762050268756</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.8675866227963</v>
       </c>
       <c r="E32">
-        <v>-26.17519771350731</v>
+        <v>-23.67852772428044</v>
       </c>
       <c r="F32">
-        <v>-0.3136457253368873</v>
+        <v>-0.3030658168683321</v>
       </c>
       <c r="G32">
-        <v>-4.777492455482594</v>
+        <v>-4.823578559934789</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.64386605720909</v>
       </c>
       <c r="E33">
-        <v>-25.53628890118712</v>
+        <v>-23.68891151518002</v>
       </c>
       <c r="F33">
-        <v>-0.4604340858477654</v>
+        <v>-0.726181803972472</v>
       </c>
       <c r="G33">
-        <v>-4.847285376541509</v>
+        <v>-4.753133461404637</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.41858786892091</v>
       </c>
       <c r="E34">
-        <v>-25.62074494143017</v>
+        <v>-23.62755974932411</v>
       </c>
       <c r="F34">
-        <v>-0.3295247000811511</v>
+        <v>-0.5223818853313208</v>
       </c>
       <c r="G34">
-        <v>-4.581518091194358</v>
+        <v>-4.282221600625467</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.19781855511027</v>
       </c>
       <c r="E35">
-        <v>-24.52959101538597</v>
+        <v>-23.33888311675715</v>
       </c>
       <c r="F35">
-        <v>-0.2266008786507153</v>
+        <v>-0.6555353183921189</v>
       </c>
       <c r="G35">
-        <v>-4.247162923364586</v>
+        <v>-3.950428795043091</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.98007034050136</v>
       </c>
       <c r="E36">
-        <v>-23.9474285108559</v>
+        <v>-22.91772597709578</v>
       </c>
       <c r="F36">
-        <v>-0.6902729054285162</v>
+        <v>-0.788432785925452</v>
       </c>
       <c r="G36">
-        <v>-3.929671674511861</v>
+        <v>-4.130539025107141</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.77186187485494</v>
       </c>
       <c r="E37">
-        <v>-23.11317038679283</v>
+        <v>-22.4667352506719</v>
       </c>
       <c r="F37">
-        <v>-0.7515207344567061</v>
+        <v>-0.7314386235106376</v>
       </c>
       <c r="G37">
-        <v>-3.585745719528056</v>
+        <v>-4.254893047198784</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.56949042289219</v>
       </c>
       <c r="E38">
-        <v>-23.4436538913986</v>
+        <v>-22.23226898045075</v>
       </c>
       <c r="F38">
-        <v>-0.8789261261094784</v>
+        <v>-0.9612782714587912</v>
       </c>
       <c r="G38">
-        <v>-4.479434108945392</v>
+        <v>-3.942020009373343</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.3738200063303</v>
       </c>
       <c r="E39">
-        <v>-22.49087201713278</v>
+        <v>-21.84097259839598</v>
       </c>
       <c r="F39">
-        <v>-1.034898596015194</v>
+        <v>-1.048304894062102</v>
       </c>
       <c r="G39">
-        <v>-2.989635647544729</v>
+        <v>-3.266185379713287</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.17193121197839</v>
       </c>
       <c r="E40">
-        <v>-21.25583035796886</v>
+        <v>-20.00860257525029</v>
       </c>
       <c r="F40">
-        <v>-0.99622046524368</v>
+        <v>-1.049717260483875</v>
       </c>
       <c r="G40">
-        <v>-3.432848173796816</v>
+        <v>-3.537911647031127</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.95714696959797</v>
       </c>
       <c r="E41">
-        <v>-21.41478432411209</v>
+        <v>-20.85164141041424</v>
       </c>
       <c r="F41">
-        <v>-1.14858125327319</v>
+        <v>-1.374284034411763</v>
       </c>
       <c r="G41">
-        <v>-3.190413613410448</v>
+        <v>-3.486184372980015</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.71410607271085</v>
       </c>
       <c r="E42">
-        <v>-20.61822121768887</v>
+        <v>-20.5997586291596</v>
       </c>
       <c r="F42">
-        <v>-1.521466697806374</v>
+        <v>-1.593420347148344</v>
       </c>
       <c r="G42">
-        <v>-3.04405108457373</v>
+        <v>-3.150382496749581</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.44169216315722</v>
       </c>
       <c r="E43">
-        <v>-20.34505460859818</v>
+        <v>-19.90114641552228</v>
       </c>
       <c r="F43">
-        <v>-1.495035150717847</v>
+        <v>-1.506378813931784</v>
       </c>
       <c r="G43">
-        <v>-2.804933690817711</v>
+        <v>-2.97446010679271</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.13006397600345</v>
       </c>
       <c r="E44">
-        <v>-20.48414668774377</v>
+        <v>-18.60305934122358</v>
       </c>
       <c r="F44">
-        <v>-1.658298082135602</v>
+        <v>-1.783972185916523</v>
       </c>
       <c r="G44">
-        <v>-2.236926839917257</v>
+        <v>-2.64491185108596</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.786676670759448</v>
       </c>
       <c r="E45">
-        <v>-18.78875394638211</v>
+        <v>-18.25469742123552</v>
       </c>
       <c r="F45">
-        <v>-1.576288052523645</v>
+        <v>-1.583932226916679</v>
       </c>
       <c r="G45">
-        <v>-2.579684172325699</v>
+        <v>-2.122047599159008</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.406511670158121</v>
       </c>
       <c r="E46">
-        <v>-19.33864654513352</v>
+        <v>-16.85409022387716</v>
       </c>
       <c r="F46">
-        <v>-1.721828891725907</v>
+        <v>-1.870706394826645</v>
       </c>
       <c r="G46">
-        <v>-2.501214311408355</v>
+        <v>-2.901316913648052</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.002044499647432</v>
       </c>
       <c r="E47">
-        <v>-18.56314989979398</v>
+        <v>-17.27378919490805</v>
       </c>
       <c r="F47">
-        <v>-1.805769017386387</v>
+        <v>-1.873184870095821</v>
       </c>
       <c r="G47">
-        <v>-2.281466919602612</v>
+        <v>-1.807774200570455</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.572327816986137</v>
       </c>
       <c r="E48">
-        <v>-17.78589620653946</v>
+        <v>-16.72879640503294</v>
       </c>
       <c r="F48">
-        <v>-1.866956375594172</v>
+        <v>-1.785137698852262</v>
       </c>
       <c r="G48">
-        <v>-2.05031138786854</v>
+        <v>-2.441700634248877</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.133446757918239</v>
       </c>
       <c r="E49">
-        <v>-17.13731004526488</v>
+        <v>-16.0019491559578</v>
       </c>
       <c r="F49">
-        <v>-2.340700521622612</v>
+        <v>-2.119632456102702</v>
       </c>
       <c r="G49">
-        <v>-2.821446691967596</v>
+        <v>-2.270350107681739</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.689954355298258</v>
       </c>
       <c r="E50">
-        <v>-16.7657895092016</v>
+        <v>-15.44629180979462</v>
       </c>
       <c r="F50">
-        <v>-2.21173282904816</v>
+        <v>-2.438591182713638</v>
       </c>
       <c r="G50">
-        <v>-2.64808997480366</v>
+        <v>-1.757851173838245</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.259851346304686</v>
       </c>
       <c r="E51">
-        <v>-16.84955722139548</v>
+        <v>-15.13432070693221</v>
       </c>
       <c r="F51">
-        <v>-2.035574702271025</v>
+        <v>-2.313142394866278</v>
       </c>
       <c r="G51">
-        <v>-2.504581136221793</v>
+        <v>-2.596173999656809</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.850190445052847</v>
       </c>
       <c r="E52">
-        <v>-15.78974486395837</v>
+        <v>-14.79315000366833</v>
       </c>
       <c r="F52">
-        <v>-2.149414749335553</v>
+        <v>-2.313330434266713</v>
       </c>
       <c r="G52">
-        <v>-2.587209042336463</v>
+        <v>-2.244547715748659</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.475557554486926</v>
       </c>
       <c r="E53">
-        <v>-15.01105564444342</v>
+        <v>-14.83761508994964</v>
       </c>
       <c r="F53">
-        <v>-2.290885819487861</v>
+        <v>-2.388759084863428</v>
       </c>
       <c r="G53">
-        <v>-2.726410861171738</v>
+        <v>-2.102783534665989</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.141279403150103</v>
       </c>
       <c r="E54">
-        <v>-14.70923285183219</v>
+        <v>-14.28455708786687</v>
       </c>
       <c r="F54">
-        <v>-2.429214892081351</v>
+        <v>-2.09435316807147</v>
       </c>
       <c r="G54">
-        <v>-2.791813998845579</v>
+        <v>-2.072922413901763</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.855771141902083</v>
       </c>
       <c r="E55">
-        <v>-14.14845380156634</v>
+        <v>-13.56113789361554</v>
       </c>
       <c r="F55">
-        <v>-2.265412693484373</v>
+        <v>-2.281295810065651</v>
       </c>
       <c r="G55">
-        <v>-2.419192235127372</v>
+        <v>-1.884449745805515</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.617688938402965</v>
       </c>
       <c r="E56">
-        <v>-13.77676118349076</v>
+        <v>-13.47578974399297</v>
       </c>
       <c r="F56">
-        <v>-2.425694330619452</v>
+        <v>-2.425585814489686</v>
       </c>
       <c r="G56">
-        <v>-2.511311475303132</v>
+        <v>-2.079738827167122</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.427437810123027</v>
       </c>
       <c r="E57">
-        <v>-13.74422409774565</v>
+        <v>-12.71760998325876</v>
       </c>
       <c r="F57">
-        <v>-2.376417238929118</v>
+        <v>-2.581685852975433</v>
       </c>
       <c r="G57">
-        <v>-3.006569087978102</v>
+        <v>-2.347227596194695</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.280005009863217</v>
       </c>
       <c r="E58">
-        <v>-12.55221199860261</v>
+        <v>-12.40181684833387</v>
       </c>
       <c r="F58">
-        <v>-2.164811614251387</v>
+        <v>-2.497229654423009</v>
       </c>
       <c r="G58">
-        <v>-2.974479970065946</v>
+        <v>-2.58885769401502</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.170316954698444</v>
       </c>
       <c r="E59">
-        <v>-13.67605697850819</v>
+        <v>-12.36606907451732</v>
       </c>
       <c r="F59">
-        <v>-2.217929845588503</v>
+        <v>-2.478645231741202</v>
       </c>
       <c r="G59">
-        <v>-3.645544103603912</v>
+        <v>-2.824462598953872</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.091748356416112</v>
       </c>
       <c r="E60">
-        <v>-11.46946292031665</v>
+        <v>-11.50922292210399</v>
       </c>
       <c r="F60">
-        <v>-2.315308575624599</v>
+        <v>-2.066786757641108</v>
       </c>
       <c r="G60">
-        <v>-2.903760096256034</v>
+        <v>-2.528787845204944</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.036443789096809</v>
       </c>
       <c r="E61">
-        <v>-12.88738247380633</v>
+        <v>-11.43368797565605</v>
       </c>
       <c r="F61">
-        <v>-2.322917958586715</v>
+        <v>-2.229927919050651</v>
       </c>
       <c r="G61">
-        <v>-3.880606079074323</v>
+        <v>-2.666099342537295</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.997386569126618</v>
       </c>
       <c r="E62">
-        <v>-10.92937446779184</v>
+        <v>-10.85163868297617</v>
       </c>
       <c r="F62">
-        <v>-2.494877090999059</v>
+        <v>-2.563687086047405</v>
       </c>
       <c r="G62">
-        <v>-3.859276234164799</v>
+        <v>-2.280801499949218</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.965976366639159</v>
       </c>
       <c r="E63">
-        <v>-10.86003447378639</v>
+        <v>-10.96956014613591</v>
       </c>
       <c r="F63">
-        <v>-2.675796673607485</v>
+        <v>-2.710472961456075</v>
       </c>
       <c r="G63">
-        <v>-4.447384717579707</v>
+        <v>-2.961976039564119</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.938557016141242</v>
       </c>
       <c r="E64">
-        <v>-11.29813263471044</v>
+        <v>-10.72753132432196</v>
       </c>
       <c r="F64">
-        <v>-2.565948529057048</v>
+        <v>-2.532484971086156</v>
       </c>
       <c r="G64">
-        <v>-4.151997981292697</v>
+        <v>-2.98854316751677</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.909495254125627</v>
       </c>
       <c r="E65">
-        <v>-10.3700173583644</v>
+        <v>-10.31432618501807</v>
       </c>
       <c r="F65">
-        <v>-2.372484978868029</v>
+        <v>-2.613834791878082</v>
       </c>
       <c r="G65">
-        <v>-4.241342984306547</v>
+        <v>-3.647940938574344</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.87856742980196</v>
       </c>
       <c r="E66">
-        <v>-10.953674259317</v>
+        <v>-10.33226347056245</v>
       </c>
       <c r="F66">
-        <v>-2.659419021686736</v>
+        <v>-2.997801307158514</v>
       </c>
       <c r="G66">
-        <v>-4.525245438117826</v>
+        <v>-3.812915354432845</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.843845902816496</v>
       </c>
       <c r="E67">
-        <v>-11.13727218100998</v>
+        <v>-9.44147640546163</v>
       </c>
       <c r="F67">
-        <v>-3.081903792829942</v>
+        <v>-2.835239174563528</v>
       </c>
       <c r="G67">
-        <v>-4.391750999792255</v>
+        <v>-3.833119613859017</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.807446076288805</v>
       </c>
       <c r="E68">
-        <v>-10.7743149892952</v>
+        <v>-10.21863047228798</v>
       </c>
       <c r="F68">
-        <v>-3.123482037878658</v>
+        <v>-2.730326442998971</v>
       </c>
       <c r="G68">
-        <v>-4.607058950029836</v>
+        <v>-4.584540619271713</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.768728262272154</v>
       </c>
       <c r="E69">
-        <v>-10.22674549770972</v>
+        <v>-9.302882458456878</v>
       </c>
       <c r="F69">
-        <v>-3.089017812085185</v>
+        <v>-3.106577544289729</v>
       </c>
       <c r="G69">
-        <v>-4.484956098904896</v>
+        <v>-3.78468633261948</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.730093471345314</v>
       </c>
       <c r="E70">
-        <v>-10.55145972642973</v>
+        <v>-10.12936972112279</v>
       </c>
       <c r="F70">
-        <v>-2.79641193765951</v>
+        <v>-3.024826793674848</v>
       </c>
       <c r="G70">
-        <v>-4.421314171457947</v>
+        <v>-3.631278962875192</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.690062490662134</v>
       </c>
       <c r="E71">
-        <v>-9.804963428635306</v>
+        <v>-9.383502881215435</v>
       </c>
       <c r="F71">
-        <v>-3.117315670932218</v>
+        <v>-3.107851573355234</v>
       </c>
       <c r="G71">
-        <v>-4.132637910979039</v>
+        <v>-3.598289376576355</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.649183061764769</v>
       </c>
       <c r="E72">
-        <v>-9.955249895527862</v>
+        <v>-8.953130296948466</v>
       </c>
       <c r="F72">
-        <v>-3.275843654275571</v>
+        <v>-3.240097115742564</v>
       </c>
       <c r="G72">
-        <v>-4.123057192188388</v>
+        <v>-3.675527714553091</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.60331244620392</v>
       </c>
       <c r="E73">
-        <v>-10.12892593067004</v>
+        <v>-9.721951971600701</v>
       </c>
       <c r="F73">
-        <v>-3.191901871880286</v>
+        <v>-3.178304220963332</v>
       </c>
       <c r="G73">
-        <v>-4.296758206088407</v>
+        <v>-2.836529537444515</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.551110694307822</v>
       </c>
       <c r="E74">
-        <v>-10.78660526775202</v>
+        <v>-9.633184824102347</v>
       </c>
       <c r="F74">
-        <v>-3.24428865480073</v>
+        <v>-3.36776095802501</v>
       </c>
       <c r="G74">
-        <v>-3.774244871988618</v>
+        <v>-3.248993716727852</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.486526942207611</v>
       </c>
       <c r="E75">
-        <v>-10.73194658647944</v>
+        <v>-9.54553168120988</v>
       </c>
       <c r="F75">
-        <v>-3.522287098445438</v>
+        <v>-3.254326810987854</v>
       </c>
       <c r="G75">
-        <v>-3.383444902714273</v>
+        <v>-2.676021047518491</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.407204196598657</v>
       </c>
       <c r="E76">
-        <v>-10.59077593776432</v>
+        <v>-10.47474737673979</v>
       </c>
       <c r="F76">
-        <v>-3.489457241537688</v>
+        <v>-3.341780871171009</v>
       </c>
       <c r="G76">
-        <v>-3.233063371592879</v>
+        <v>-2.378538735905122</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.306479669047123</v>
       </c>
       <c r="E77">
-        <v>-11.13767974367067</v>
+        <v>-10.695673509678</v>
       </c>
       <c r="F77">
-        <v>-3.596914717763645</v>
+        <v>-3.520096895032436</v>
       </c>
       <c r="G77">
-        <v>-1.891183395432392</v>
+        <v>-2.344539433216807</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.184875553462367</v>
       </c>
       <c r="E78">
-        <v>-11.57446011865849</v>
+        <v>-11.06007981307523</v>
       </c>
       <c r="F78">
-        <v>-3.665901983436191</v>
+        <v>-3.8690383797877</v>
       </c>
       <c r="G78">
-        <v>-2.965326311649861</v>
+        <v>-1.953524278482408</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.040340565167792</v>
       </c>
       <c r="E79">
-        <v>-12.24843290522007</v>
+        <v>-11.08736839744545</v>
       </c>
       <c r="F79">
-        <v>-3.709270330442356</v>
+        <v>-3.833397872282251</v>
       </c>
       <c r="G79">
-        <v>-2.218460616899203</v>
+        <v>-1.923388382438422</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.880205277851081</v>
       </c>
       <c r="E80">
-        <v>-12.04274055884367</v>
+        <v>-11.86879281526103</v>
       </c>
       <c r="F80">
-        <v>-4.03820011548079</v>
+        <v>-3.886941884464405</v>
       </c>
       <c r="G80">
-        <v>-1.972834690612977</v>
+        <v>-1.618146152081001</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.710060352962754</v>
       </c>
       <c r="E81">
-        <v>-13.81418902116416</v>
+        <v>-12.01457797898997</v>
       </c>
       <c r="F81">
-        <v>-3.993046636721592</v>
+        <v>-3.833024278583589</v>
       </c>
       <c r="G81">
-        <v>-1.709864816246509</v>
+        <v>-1.406469870300001</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.542053783986099</v>
       </c>
       <c r="E82">
-        <v>-14.06345887291637</v>
+        <v>-13.47895061885033</v>
       </c>
       <c r="F82">
-        <v>-3.906913822545901</v>
+        <v>-3.902630334706025</v>
       </c>
       <c r="G82">
-        <v>-1.552719840588385</v>
+        <v>-1.421430225591968</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.387832693704912</v>
       </c>
       <c r="E83">
-        <v>-14.19688583107837</v>
+        <v>-14.49725951200715</v>
       </c>
       <c r="F83">
-        <v>-4.473963616090872</v>
+        <v>-4.025136761538642</v>
       </c>
       <c r="G83">
-        <v>-1.592601982699985</v>
+        <v>-0.6478947759769409</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.263051008393312</v>
       </c>
       <c r="E84">
-        <v>-16.33204774027292</v>
+        <v>-15.56137391975155</v>
       </c>
       <c r="F84">
-        <v>-4.257803627432549</v>
+        <v>-4.354645575391632</v>
       </c>
       <c r="G84">
-        <v>-0.3917280726936757</v>
+        <v>-0.1955782494918578</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.183364039861626</v>
       </c>
       <c r="E85">
-        <v>-16.19306887297752</v>
+        <v>-16.23153825967268</v>
       </c>
       <c r="F85">
-        <v>-4.763709966242083</v>
+        <v>-4.355596541170045</v>
       </c>
       <c r="G85">
-        <v>-1.144138931222613</v>
+        <v>-0.5971209390411386</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.163465872208767</v>
       </c>
       <c r="E86">
-        <v>-18.01486490931529</v>
+        <v>-17.59665580623292</v>
       </c>
       <c r="F86">
-        <v>-4.96565931210538</v>
+        <v>-4.613263535280443</v>
       </c>
       <c r="G86">
-        <v>-0.4769812414209872</v>
+        <v>0.3039433458376931</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.219212246064957</v>
       </c>
       <c r="E87">
-        <v>-18.98648523545302</v>
+        <v>-18.16973872037762</v>
       </c>
       <c r="F87">
-        <v>-4.992726216991854</v>
+        <v>-4.822234123249869</v>
       </c>
       <c r="G87">
-        <v>-0.1510116854421891</v>
+        <v>0.343739413765272</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.358914913304136</v>
       </c>
       <c r="E88">
-        <v>-19.58023157649472</v>
+        <v>-19.6936924927569</v>
       </c>
       <c r="F88">
-        <v>-5.213870492312822</v>
+        <v>-4.97024266894507</v>
       </c>
       <c r="G88">
-        <v>-0.4676653662734782</v>
+        <v>0.3605338112859947</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.595182411660429</v>
       </c>
       <c r="E89">
-        <v>-20.63083301780023</v>
+        <v>-20.84398376086727</v>
       </c>
       <c r="F89">
-        <v>-5.357579811187493</v>
+        <v>-5.117619998679339</v>
       </c>
       <c r="G89">
-        <v>-0.2480007381062171</v>
+        <v>-0.2427667656086293</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.928034616343435</v>
       </c>
       <c r="E90">
-        <v>-23.25216283951026</v>
+        <v>-21.9552893962456</v>
       </c>
       <c r="F90">
-        <v>-5.362112637615613</v>
+        <v>-5.239278177291488</v>
       </c>
       <c r="G90">
-        <v>-0.3071734290751503</v>
+        <v>0.1764145105738884</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.366980389075596</v>
       </c>
       <c r="E91">
-        <v>-24.43202957136472</v>
+        <v>-24.48107294486779</v>
       </c>
       <c r="F91">
-        <v>-5.674466790924028</v>
+        <v>-5.816255125791608</v>
       </c>
       <c r="G91">
-        <v>-0.6464745519405936</v>
+        <v>0.1772653207774811</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.903274166511424</v>
       </c>
       <c r="E92">
-        <v>-26.50761034804036</v>
+        <v>-25.8544911842841</v>
       </c>
       <c r="F92">
-        <v>-5.793610874468681</v>
+        <v>-6.048168177348969</v>
       </c>
       <c r="G92">
-        <v>-0.2128361233880785</v>
+        <v>0.332496801113907</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.542400113853632</v>
       </c>
       <c r="E93">
-        <v>-28.89532978111669</v>
+        <v>-27.79222068369224</v>
       </c>
       <c r="F93">
-        <v>-5.748165810383697</v>
+        <v>-6.152128286400306</v>
       </c>
       <c r="G93">
-        <v>-1.178929454294814</v>
+        <v>-0.6788583084057442</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.266883059417091</v>
       </c>
       <c r="E94">
-        <v>-29.49016522015722</v>
+        <v>-29.46885195724012</v>
       </c>
       <c r="F94">
-        <v>-5.437986949875033</v>
+        <v>-6.156356273624196</v>
       </c>
       <c r="G94">
-        <v>-1.313956675205068</v>
+        <v>-0.9620986531091692</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.072496097502201</v>
       </c>
       <c r="E95">
-        <v>-32.69694069005288</v>
+        <v>-32.4740831629504</v>
       </c>
       <c r="F95">
-        <v>-6.008810785307158</v>
+        <v>-6.37778385059692</v>
       </c>
       <c r="G95">
-        <v>-2.550461986850553</v>
+        <v>-1.768444919563913</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.94092413822745</v>
       </c>
       <c r="E96">
-        <v>-34.00113894002494</v>
+        <v>-34.23876382086643</v>
       </c>
       <c r="F96">
-        <v>-6.046826222156434</v>
+        <v>-6.112394815557626</v>
       </c>
       <c r="G96">
-        <v>-3.293858229876055</v>
+        <v>-2.485691163374712</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.851621971884445</v>
       </c>
       <c r="E97">
-        <v>-36.33429931825686</v>
+        <v>-36.39320570814863</v>
       </c>
       <c r="F97">
-        <v>-6.159830446511537</v>
+        <v>-6.671347317740231</v>
       </c>
       <c r="G97">
-        <v>-3.656492077702282</v>
+        <v>-1.965332994420988</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.797722826898674</v>
       </c>
       <c r="E98">
-        <v>-38.87059345505085</v>
+        <v>-38.79169158817821</v>
       </c>
       <c r="F98">
-        <v>-6.380709230079907</v>
+        <v>-6.571576676828552</v>
       </c>
       <c r="G98">
-        <v>-3.179667582589974</v>
+        <v>-3.267469871382524</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.73707287144044</v>
       </c>
       <c r="E99">
-        <v>-41.57390450595874</v>
+        <v>-41.2610345010058</v>
       </c>
       <c r="F99">
-        <v>-6.432252320800599</v>
+        <v>-6.787409460362769</v>
       </c>
       <c r="G99">
-        <v>-3.882360668210137</v>
+        <v>-3.514075719148374</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.69793128072945</v>
       </c>
       <c r="E100">
-        <v>-43.48835538473045</v>
+        <v>-43.17782660083947</v>
       </c>
       <c r="F100">
-        <v>-6.363256771454025</v>
+        <v>-6.63121126033979</v>
       </c>
       <c r="G100">
-        <v>-5.30533576790061</v>
+        <v>-4.559105697893492</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.59545731533196</v>
       </c>
       <c r="E101">
-        <v>-46.15420463440988</v>
+        <v>-45.45066770528922</v>
       </c>
       <c r="F101">
-        <v>-6.461803499528068</v>
+        <v>-6.810924325826038</v>
       </c>
       <c r="G101">
-        <v>-5.827875586364714</v>
+        <v>-4.936345672638983</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.55107817795948</v>
       </c>
       <c r="E102">
-        <v>-47.93260430433214</v>
+        <v>-48.00383267199879</v>
       </c>
       <c r="F102">
-        <v>-6.546861921182328</v>
+        <v>-7.023446539034967</v>
       </c>
       <c r="G102">
-        <v>-6.541377603170597</v>
+        <v>-5.419592626097477</v>
       </c>
     </row>
   </sheetData>
